--- a/Data/FlightPlan/FPL_11AUG26.xlsx
+++ b/Data/FlightPlan/FPL_11AUG26.xlsx
@@ -311,6 +311,9 @@
     <t>12:55</t>
   </si>
   <si>
+    <t>13:51</t>
+  </si>
+  <si>
     <t>14:10</t>
   </si>
   <si>
@@ -356,825 +359,849 @@
     <t>11:10</t>
   </si>
   <si>
+    <t>11:06</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>VN-A526</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>07:03</t>
+  </si>
+  <si>
+    <t>CXR</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>NOZ</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>00:15</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>VN-A534</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>08:54</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>21:35</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:45</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>VN-A537</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>VN-A539</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>09:45</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>21:40</t>
+  </si>
+  <si>
+    <t>23:50</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>VN-A547</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>HGH</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>03:10</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>VN-A550</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>06:31</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>08:42</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>22:55</t>
+  </si>
+  <si>
+    <t>00:05</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>HYD</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>09:31</t>
+  </si>
+  <si>
+    <t>ZHA</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>DPS</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>BOM</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>10:41</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>08:32</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>19:10</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>10:22</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>07:37</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>23:40</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
     <t>11:15</t>
   </si>
   <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>VN-A526</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>07:03</t>
-  </si>
-  <si>
-    <t>CXR</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>NOZ</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>00:15</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>VN-A529</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A534</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>08:50</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>21:35</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>01:45</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>VN-A537</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>VN-A539</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>07:50</t>
-  </si>
-  <si>
-    <t>09:45</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>21:40</t>
-  </si>
-  <si>
-    <t>23:50</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>09:30</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>VN-A547</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>13:35</t>
-  </si>
-  <si>
-    <t>HGH</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>03:10</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>VN-A550</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>06:31</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>22:55</t>
-  </si>
-  <si>
-    <t>00:05</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>HYD</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>09:31</t>
-  </si>
-  <si>
-    <t>ZHA</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>DPS</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>BOM</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>08:32</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>19:10</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>11:22</t>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>07:18</t>
   </si>
   <si>
     <t>12:35</t>
   </si>
   <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>14:45</t>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>06:43</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>10:01</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>TSN</t>
+  </si>
+  <si>
+    <t>03:15</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>10:25</t>
   </si>
   <si>
     <t>15:15</t>
   </si>
   <si>
-    <t>18:25</t>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>08:14</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>00:45</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>08:18</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A662</t>
+  </si>
+  <si>
+    <t>07:11</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>VN-A666</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>06:47</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>07:39</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>VN-A671</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>ENH</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
   </si>
   <si>
     <t>21:05</t>
   </si>
   <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>07:37</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>23:40</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>06:43</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>10:01</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>TSN</t>
-  </si>
-  <si>
-    <t>03:15</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>15:35</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>07:05</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>00:45</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A662</t>
-  </si>
-  <si>
-    <t>07:27</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>VN-A666</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>06:47</t>
-  </si>
-  <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>07:51</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>VN-A671</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>ENH</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
     <t>02:40</t>
   </si>
   <si>
@@ -1196,6 +1223,9 @@
     <t>HIJ</t>
   </si>
   <si>
+    <t>12:19</t>
+  </si>
+  <si>
     <t>PKX</t>
   </si>
   <si>
@@ -1235,10 +1265,7 @@
     <t>VN-A687</t>
   </si>
   <si>
-    <t>07:52</t>
-  </si>
-  <si>
-    <t>15:00</t>
+    <t>08:02</t>
   </si>
   <si>
     <t>VN-A689</t>
@@ -1319,7 +1346,7 @@
     <t>Total Record(s): 427</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 11, 2026 06:06</t>
+    <t xml:space="preserve">Generated on  Aug 11, 2026 06:55</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3114,7 +3141,9 @@
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
-      <c r="M48" s="7"/>
+      <c t="s" r="M48" s="7">
+        <v>100</v>
+      </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c t="s" r="A49" s="6">
@@ -3140,10 +3169,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -3176,7 +3205,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3206,7 +3235,7 @@
         <v>56</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J51" s="7">
         <v>57</v>
@@ -3242,7 +3271,7 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
@@ -3254,7 +3283,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J53" s="7">
         <v>83</v>
@@ -3275,7 +3304,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3287,7 +3316,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J54" s="7">
         <v>92</v>
@@ -3308,7 +3337,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3320,10 +3349,10 @@
         <v>77</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3341,7 +3370,7 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
@@ -3353,10 +3382,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3389,27 +3418,27 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G58" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H58" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
       <c t="s" r="M58" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
@@ -3424,7 +3453,7 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
@@ -3433,13 +3462,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H59" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -3457,22 +3486,22 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G60" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="H60" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3490,7 +3519,7 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
@@ -3502,10 +3531,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
@@ -3538,7 +3567,7 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -3550,15 +3579,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
       <c t="s" r="M63" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
@@ -3573,7 +3602,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3582,13 +3611,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H64" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -3602,26 +3631,26 @@
         <v>5068</v>
       </c>
       <c t="s" r="C65" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G65" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H65" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
@@ -3635,11 +3664,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C66" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -3648,13 +3677,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H66" s="8">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -3668,26 +3697,26 @@
         <v>5069</v>
       </c>
       <c t="s" r="C67" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G67" s="8">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c t="s" r="H67" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3720,7 +3749,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -3729,13 +3758,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H69" s="8">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="I69" s="7">
         <v>67</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3753,22 +3782,22 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G70" s="8">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="H70" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3779,14 +3808,14 @@
         <v>13</v>
       </c>
       <c r="B71" s="7">
-        <v>3908</v>
+        <v>284</v>
       </c>
       <c t="s" r="C71" s="7">
         <v>14</v>
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -3795,13 +3824,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H71" s="8">
-        <v>138</v>
+        <v>49</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3809,32 +3838,32 @@
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c t="s" r="A72" s="6">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B72" s="7">
-        <v>3909</v>
+        <v>926</v>
       </c>
       <c t="s" r="C72" s="7">
         <v>14</v>
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
+        <v>135</v>
+      </c>
+      <c r="F72" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G72" s="8">
+        <v>49</v>
+      </c>
+      <c t="s" r="H72" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I72" s="7">
+        <v>141</v>
+      </c>
+      <c t="s" r="J72" s="7">
         <v>134</v>
-      </c>
-      <c r="F72" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G72" s="8">
-        <v>138</v>
-      </c>
-      <c t="s" r="H72" s="8">
-        <v>21</v>
-      </c>
-      <c t="s" r="I72" s="7">
-        <v>140</v>
-      </c>
-      <c t="s" r="J72" s="7">
-        <v>141</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -3886,7 +3915,9 @@
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
-      <c r="M74" s="7"/>
+      <c t="s" r="M74" s="7">
+        <v>146</v>
+      </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c t="s" r="A75" s="6">
@@ -3945,10 +3976,10 @@
         <v>77</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -3978,10 +4009,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -4011,10 +4042,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -4044,10 +4075,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -4074,13 +4105,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -4104,13 +4135,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="H81" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c t="s" r="J81" s="7">
         <v>157</v>
@@ -4191,7 +4222,7 @@
         <v>162</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J84" s="7">
         <v>94</v>
@@ -4224,7 +4255,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J85" s="7">
         <v>163</v>
@@ -4254,7 +4285,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I86" s="7">
         <v>164</v>
@@ -4341,7 +4372,7 @@
         <v>169</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4371,10 +4402,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4507,7 +4538,9 @@
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
-      <c r="M95" s="7"/>
+      <c t="s" r="M95" s="7">
+        <v>34</v>
+      </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
       <c t="s" r="A96" s="6">
@@ -4629,7 +4662,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H99" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I99" s="7">
         <v>180</v>
@@ -4659,13 +4692,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G100" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H100" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="J100" s="7">
         <v>182</v>
@@ -4782,7 +4815,7 @@
         <v>187</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4815,7 +4848,7 @@
         <v>51</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -5022,7 +5055,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="I112" s="7">
         <v>92</v>
@@ -5052,13 +5085,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="J113" s="7">
         <v>199</v>
@@ -5208,7 +5241,7 @@
         <v>206</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5241,7 +5274,7 @@
         <v>207</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5280,10 +5313,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I121" s="7">
         <v>209</v>
@@ -5313,13 +5346,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H122" s="8">
         <v>211</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>212</v>
@@ -5349,10 +5382,10 @@
         <v>211</v>
       </c>
       <c t="s" r="H123" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J123" s="7">
         <v>74</v>
@@ -5379,10 +5412,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G124" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I124" s="7">
         <v>213</v>
@@ -5678,10 +5711,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>224</v>
@@ -5708,7 +5741,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G135" s="8">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="H135" s="8">
         <v>21</v>
@@ -5769,7 +5802,9 @@
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
-      <c r="M137" s="7"/>
+      <c t="s" r="M137" s="7">
+        <v>228</v>
+      </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
       <c t="s" r="A138" s="6">
@@ -5798,7 +5833,7 @@
         <v>197</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5828,10 +5863,10 @@
         <v>77</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5861,10 +5896,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5894,10 +5929,10 @@
         <v>176</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5963,7 +5998,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5972,10 +6007,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>50</v>
@@ -5996,13 +6031,13 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="H145" s="8">
         <v>43</v>
@@ -6011,7 +6046,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -6029,7 +6064,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6038,13 +6073,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H146" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="I146" s="7">
         <v>191</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6062,22 +6097,22 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G147" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="H147" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6110,7 +6145,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6122,7 +6157,7 @@
         <v>162</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J149" s="7">
         <v>171</v>
@@ -6143,7 +6178,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6158,7 +6193,7 @@
         <v>58</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6176,7 +6211,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6185,13 +6220,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H151" s="8">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="I151" s="7">
         <v>72</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6209,22 +6244,22 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G152" s="8">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="H152" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6257,7 +6292,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6266,7 +6301,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I154" s="7">
         <v>227</v>
@@ -6277,7 +6312,7 @@
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -6292,22 +6327,22 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="I155" s="7">
         <v>51</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6325,22 +6360,22 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6354,17 +6389,17 @@
         <v>7706</v>
       </c>
       <c t="s" r="C157" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>43</v>
@@ -6387,11 +6422,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C158" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6400,7 +6435,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="I158" s="7">
         <v>164</v>
@@ -6439,7 +6474,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6472,7 +6507,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6481,10 +6516,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H161" s="8">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="J161" s="7">
         <v>181</v>
@@ -6505,19 +6540,19 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G162" s="8">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="H162" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="J162" s="7">
         <v>53</v>
@@ -6538,7 +6573,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6586,13 +6621,13 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>21</v>
@@ -6601,7 +6636,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6619,7 +6654,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6631,10 +6666,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6652,7 +6687,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6664,10 +6699,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6685,7 +6720,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6694,13 +6729,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6733,7 +6768,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6742,7 +6777,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="I170" s="7">
         <v>186</v>
@@ -6755,7 +6790,7 @@
       </c>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -6770,29 +6805,29 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="H171" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="J171" s="7">
         <v>70</v>
       </c>
       <c t="s" r="K171" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -6807,7 +6842,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6816,13 +6851,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="I172" s="7">
         <v>191</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -6840,22 +6875,22 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6888,7 +6923,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6897,7 +6932,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="I175" s="7">
         <v>57</v>
@@ -6921,13 +6956,13 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>21</v>
@@ -6954,7 +6989,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6966,7 +7001,7 @@
         <v>61</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="J177" s="7">
         <v>200</v>
@@ -6987,7 +7022,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -6999,10 +7034,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7035,13 +7070,13 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G180" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H180" s="8">
         <v>43</v>
@@ -7050,11 +7085,13 @@
         <v>46</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
-      <c r="M180" s="7"/>
+      <c t="s" r="M180" s="7">
+        <v>267</v>
+      </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
       <c t="s" r="A181" s="6">
@@ -7068,7 +7105,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7077,7 +7114,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I181" s="7">
         <v>206</v>
@@ -7101,22 +7138,22 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7134,7 +7171,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7167,7 +7204,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7179,10 +7216,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7200,7 +7237,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7212,7 +7249,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>79</v>
@@ -7233,7 +7270,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7242,7 +7279,7 @@
         <v>77</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I186" s="7">
         <v>27</v>
@@ -7281,7 +7318,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7293,7 +7330,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J188" s="7">
         <v>98</v>
@@ -7301,7 +7338,7 @@
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -7316,7 +7353,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7325,10 +7362,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J189" s="7">
         <v>50</v>
@@ -7349,13 +7386,13 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="H190" s="8">
         <v>43</v>
@@ -7382,7 +7419,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7397,7 +7434,7 @@
         <v>94</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7415,7 +7452,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7430,7 +7467,7 @@
         <v>191</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7463,7 +7500,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7472,10 +7509,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J194" s="7">
         <v>33</v>
@@ -7498,22 +7535,22 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H195" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7531,7 +7568,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7564,7 +7601,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7597,7 +7634,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7606,10 +7643,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J198" s="7">
         <v>60</v>
@@ -7630,13 +7667,13 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H199" s="8">
         <v>43</v>
@@ -7645,7 +7682,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7678,7 +7715,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7690,17 +7727,17 @@
         <v>49</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c t="s" r="K201" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -7708,14 +7745,14 @@
         <v>13</v>
       </c>
       <c r="B202" s="7">
-        <v>671</v>
+        <v>7078</v>
       </c>
       <c t="s" r="C202" s="7">
         <v>14</v>
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7724,72 +7761,64 @@
         <v>49</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>176</v>
+        <v>283</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>209</v>
+        <v>284</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>281</v>
-      </c>
-      <c t="s" r="K202" s="7">
-        <v>282</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="K202" s="7"/>
       <c r="L202" s="7"/>
-      <c t="s" r="M202" s="7">
-        <v>210</v>
-      </c>
+      <c r="M202" s="7"/>
     </row>
     <row r="203" ht="14.25" customHeight="1">
       <c t="s" r="A203" s="6">
         <v>13</v>
       </c>
       <c r="B203" s="7">
-        <v>670</v>
+        <v>7079</v>
       </c>
       <c t="s" r="C203" s="7">
         <v>14</v>
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>176</v>
+        <v>283</v>
       </c>
       <c t="s" r="H203" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>283</v>
-      </c>
-      <c t="s" r="K203" s="7">
-        <v>229</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="K203" s="7"/>
       <c r="L203" s="7"/>
-      <c t="s" r="M203" s="7">
-        <v>86</v>
-      </c>
+      <c r="M203" s="7"/>
     </row>
     <row r="204" ht="14.25" customHeight="1">
       <c t="s" r="A204" s="6">
         <v>13</v>
       </c>
       <c r="B204" s="7">
-        <v>489</v>
+        <v>273</v>
       </c>
       <c t="s" r="C204" s="7">
         <v>14</v>
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7798,87 +7827,79 @@
         <v>49</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>226</v>
+        <v>21</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>284</v>
+        <v>181</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>149</v>
-      </c>
-      <c t="s" r="K204" s="7">
-        <v>101</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="K204" s="7"/>
       <c r="L204" s="7"/>
-      <c t="s" r="M204" s="7">
-        <v>285</v>
-      </c>
+      <c r="M204" s="7"/>
     </row>
     <row r="205" ht="15" customHeight="1">
       <c t="s" r="A205" s="6">
         <v>13</v>
       </c>
       <c r="B205" s="7">
-        <v>488</v>
+        <v>3908</v>
       </c>
       <c t="s" r="C205" s="7">
         <v>14</v>
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>226</v>
+        <v>21</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>49</v>
+        <v>286</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>120</v>
-      </c>
-      <c t="s" r="K205" s="7">
-        <v>102</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="K205" s="7"/>
       <c r="L205" s="7"/>
-      <c t="s" r="M205" s="7">
-        <v>286</v>
-      </c>
+      <c r="M205" s="7"/>
     </row>
     <row r="206" ht="14.25" customHeight="1">
       <c t="s" r="A206" s="6">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B206" s="7">
-        <v>926</v>
+        <v>3909</v>
       </c>
       <c t="s" r="C206" s="7">
         <v>14</v>
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>49</v>
+        <v>286</v>
       </c>
       <c t="s" r="H206" s="8">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>156</v>
+        <v>288</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>133</v>
+        <v>289</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7911,22 +7932,22 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7944,7 +7965,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7953,13 +7974,13 @@
         <v>49</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I209" s="7">
         <v>99</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7977,22 +7998,22 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -8010,7 +8031,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8019,7 +8040,7 @@
         <v>49</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I211" s="7">
         <v>191</v>
@@ -8043,22 +8064,22 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H212" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>290</v>
+        <v>140</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8091,7 +8112,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8103,15 +8124,15 @@
         <v>143</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -8126,7 +8147,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8141,7 +8162,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8159,7 +8180,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8171,7 +8192,7 @@
         <v>66</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>38</v>
@@ -8192,7 +8213,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8204,7 +8225,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J217" s="7">
         <v>59</v>
@@ -8225,7 +8246,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8234,13 +8255,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8258,13 +8279,13 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>21</v>
@@ -8273,7 +8294,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8291,7 +8312,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8303,7 +8324,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J220" s="7">
         <v>73</v>
@@ -8324,7 +8345,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8336,7 +8357,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="J221" s="7">
         <v>200</v>
@@ -8372,7 +8393,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8381,17 +8402,19 @@
         <v>21</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>46</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
-      <c r="M223" s="7"/>
+      <c t="s" r="M223" s="7">
+        <v>57</v>
+      </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
       <c t="s" r="A224" s="6">
@@ -8405,19 +8428,19 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J224" s="7">
         <v>204</v>
@@ -8438,7 +8461,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8447,10 +8470,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>115</v>
+        <v>301</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>179</v>
@@ -8471,22 +8494,22 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8504,7 +8527,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8516,10 +8539,10 @@
         <v>216</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8537,7 +8560,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8549,10 +8572,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8570,7 +8593,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8582,10 +8605,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8618,7 +8641,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8627,7 +8650,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c t="s" r="I231" s="7">
         <v>145</v>
@@ -8651,22 +8674,22 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>282</v>
+        <v>310</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8684,7 +8707,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8696,7 +8719,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>59</v>
@@ -8717,7 +8740,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8732,7 +8755,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8750,7 +8773,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8783,7 +8806,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8795,10 +8818,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8831,7 +8854,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8846,11 +8869,13 @@
         <v>173</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
-      <c r="M238" s="7"/>
+      <c t="s" r="M238" s="7">
+        <v>315</v>
+      </c>
     </row>
     <row r="239" ht="14.25" customHeight="1">
       <c t="s" r="A239" s="6">
@@ -8864,7 +8889,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8897,7 +8922,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8909,7 +8934,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="J240" s="7">
         <v>205</v>
@@ -8930,7 +8955,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8942,7 +8967,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="J241" s="7">
         <v>171</v>
@@ -8963,7 +8988,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8975,10 +9000,10 @@
         <v>143</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8996,7 +9021,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9008,10 +9033,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -9044,7 +9069,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9053,17 +9078,19 @@
         <v>77</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
-      <c r="M245" s="7"/>
+      <c t="s" r="M245" s="7">
+        <v>319</v>
+      </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
       <c t="s" r="A246" s="6">
@@ -9077,13 +9104,13 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H246" s="8">
         <v>77</v>
@@ -9110,7 +9137,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9143,7 +9170,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9158,7 +9185,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>281</v>
+        <v>320</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9176,7 +9203,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9188,10 +9215,10 @@
         <v>226</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9209,7 +9236,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9221,7 +9248,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="J250" s="7">
         <v>39</v>
@@ -9242,7 +9269,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9254,10 +9281,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9275,7 +9302,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9287,10 +9314,10 @@
         <v>77</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9308,7 +9335,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9320,10 +9347,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9356,7 +9383,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9365,7 +9392,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="I255" s="7">
         <v>18</v>
@@ -9376,7 +9403,7 @@
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -9391,19 +9418,19 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="H256" s="8">
         <v>176</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c t="s" r="J256" s="7">
         <v>186</v>
@@ -9424,7 +9451,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9433,13 +9460,13 @@
         <v>176</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="I257" s="7">
         <v>160</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9457,19 +9484,19 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J258" s="7">
         <v>50</v>
@@ -9490,7 +9517,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9505,7 +9532,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9523,7 +9550,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9535,10 +9562,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9556,7 +9583,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9568,10 +9595,10 @@
         <v>77</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9589,7 +9616,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9601,10 +9628,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9637,13 +9664,13 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H264" s="8">
         <v>43</v>
@@ -9670,7 +9697,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9703,7 +9730,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9718,7 +9745,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9736,7 +9763,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9751,7 +9778,7 @@
         <v>189</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9769,7 +9796,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9784,7 +9811,7 @@
         <v>163</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9802,7 +9829,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9814,10 +9841,10 @@
         <v>77</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9850,7 +9877,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9862,10 +9889,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9885,7 +9912,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -9894,7 +9921,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="I272" s="7">
         <v>57</v>
@@ -9918,13 +9945,13 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>21</v>
@@ -9933,7 +9960,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9951,7 +9978,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -9966,7 +9993,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9984,7 +10011,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -9996,7 +10023,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>223</v>
@@ -10017,7 +10044,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10050,7 +10077,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10065,7 +10092,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10098,7 +10125,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -10110,7 +10137,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>30</v>
@@ -10118,7 +10145,7 @@
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>327</v>
+        <v>334</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10133,7 +10160,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10142,13 +10169,13 @@
         <v>77</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>328</v>
+        <v>283</v>
       </c>
       <c t="s" r="I280" s="7">
         <v>178</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10166,13 +10193,13 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>328</v>
+        <v>283</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>77</v>
@@ -10181,7 +10208,7 @@
         <v>198</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10199,7 +10226,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -10208,13 +10235,13 @@
         <v>77</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>328</v>
+        <v>283</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10232,22 +10259,22 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>328</v>
+        <v>283</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>77</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10280,7 +10307,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10292,7 +10319,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>30</v>
@@ -10313,7 +10340,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10325,7 +10352,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J286" s="7">
         <v>24</v>
@@ -10346,7 +10373,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10355,13 +10382,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="I287" s="7">
         <v>37</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10379,13 +10406,13 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="H288" s="8">
         <v>21</v>
@@ -10394,7 +10421,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10412,7 +10439,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10427,7 +10454,7 @@
         <v>190</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10445,7 +10472,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10454,13 +10481,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10493,7 +10520,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -10502,13 +10529,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10526,13 +10553,13 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>21</v>
@@ -10541,7 +10568,7 @@
         <v>171</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>284</v>
+        <v>342</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10559,7 +10586,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -10568,7 +10595,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c t="s" r="I294" s="7">
         <v>59</v>
@@ -10592,22 +10619,22 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10640,7 +10667,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
@@ -10652,10 +10679,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10673,7 +10700,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
@@ -10706,7 +10733,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -10715,13 +10742,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10739,13 +10766,13 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>21</v>
@@ -10772,7 +10799,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -10781,10 +10808,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>25</v>
@@ -10805,22 +10832,22 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10853,7 +10880,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -10865,7 +10892,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>210</v>
@@ -10886,7 +10913,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -10895,13 +10922,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10919,13 +10946,13 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c t="s" r="H306" s="8">
         <v>43</v>
@@ -10934,7 +10961,7 @@
         <v>95</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10952,7 +10979,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -10964,10 +10991,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -11000,7 +11027,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -11012,7 +11039,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>19</v>
@@ -11033,7 +11060,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -11066,7 +11093,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -11099,7 +11126,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -11114,7 +11141,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11132,7 +11159,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -11144,10 +11171,10 @@
         <v>188</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11165,7 +11192,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -11177,7 +11204,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J314" s="7">
         <v>60</v>
@@ -11198,7 +11225,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
@@ -11210,10 +11237,10 @@
         <v>77</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11231,7 +11258,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -11243,10 +11270,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11279,7 +11306,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11291,14 +11318,16 @@
         <v>43</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
-      <c r="M318" s="7"/>
+      <c t="s" r="M318" s="7">
+        <v>360</v>
+      </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
       <c t="s" r="A319" s="6">
@@ -11312,7 +11341,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11345,7 +11374,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11354,7 +11383,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="I320" s="7">
         <v>187</v>
@@ -11378,13 +11407,13 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>21</v>
@@ -11393,7 +11422,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11411,7 +11440,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11423,10 +11452,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11444,7 +11473,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11456,10 +11485,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11477,7 +11506,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11489,10 +11518,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11525,7 +11554,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="F326" s="7">
         <v>321</v>
@@ -11537,7 +11566,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>145</v>
@@ -11558,7 +11587,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -11573,7 +11602,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11591,7 +11620,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -11603,10 +11632,10 @@
         <v>77</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11624,7 +11653,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -11639,7 +11668,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11657,7 +11686,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -11672,7 +11701,7 @@
         <v>51</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11690,7 +11719,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -11702,10 +11731,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11723,7 +11752,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -11756,7 +11785,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -11768,10 +11797,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11804,7 +11833,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -11816,7 +11845,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>46</v>
@@ -11824,7 +11853,7 @@
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
       <c t="s" r="M335" s="7">
-        <v>276</v>
+        <v>366</v>
       </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
@@ -11839,7 +11868,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -11854,7 +11883,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11872,7 +11901,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -11887,7 +11916,7 @@
         <v>171</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11905,7 +11934,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -11917,7 +11946,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>163</v>
@@ -11938,7 +11967,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -11950,10 +11979,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11986,7 +12015,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -11995,13 +12024,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c t="s" r="I341" s="7">
         <v>197</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>281</v>
+        <v>320</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -12019,13 +12048,13 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c t="s" r="H342" s="8">
         <v>21</v>
@@ -12034,7 +12063,7 @@
         <v>210</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -12052,7 +12081,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -12064,10 +12093,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -12085,7 +12114,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
@@ -12100,7 +12129,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -12118,7 +12147,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -12133,7 +12162,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12151,7 +12180,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12163,10 +12192,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12199,7 +12228,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -12211,10 +12240,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12232,7 +12261,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -12247,7 +12276,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12265,7 +12294,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -12280,7 +12309,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12298,7 +12327,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -12307,10 +12336,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>189</v>
@@ -12331,22 +12360,22 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12364,7 +12393,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12373,10 +12402,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>224</v>
@@ -12397,13 +12426,13 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>43</v>
@@ -12412,7 +12441,7 @@
         <v>192</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12445,7 +12474,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -12457,15 +12486,15 @@
         <v>77</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -12480,7 +12509,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12492,7 +12521,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>145</v>
@@ -12513,7 +12542,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12522,13 +12551,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="I358" s="7">
         <v>91</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12546,19 +12575,19 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>24</v>
@@ -12579,7 +12608,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12588,10 +12617,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c t="s" r="J360" s="7">
         <v>69</v>
@@ -12612,13 +12641,13 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>43</v>
@@ -12645,7 +12674,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12657,10 +12686,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12678,7 +12707,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12687,13 +12716,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12711,22 +12740,22 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12759,7 +12788,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -12771,15 +12800,15 @@
         <v>49</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>369</v>
+        <v>378</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -12794,7 +12823,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -12809,7 +12838,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12827,7 +12856,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -12842,7 +12871,7 @@
         <v>30</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12860,7 +12889,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -12893,7 +12922,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
@@ -12905,10 +12934,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12926,7 +12955,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -12941,7 +12970,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12959,7 +12988,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -13007,13 +13036,13 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c t="s" r="H374" s="8">
         <v>43</v>
@@ -13040,7 +13069,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -13049,7 +13078,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="I375" s="7">
         <v>86</v>
@@ -13073,13 +13102,13 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>43</v>
@@ -13088,7 +13117,7 @@
         <v>190</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13121,7 +13150,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -13154,7 +13183,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -13187,7 +13216,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
@@ -13220,7 +13249,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
@@ -13232,10 +13261,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13253,7 +13282,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -13262,13 +13291,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13286,13 +13315,13 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c t="s" r="H383" s="8">
         <v>43</v>
@@ -13301,7 +13330,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13334,7 +13363,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13343,18 +13372,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
       <c t="s" r="M385" s="7">
-        <v>376</v>
+        <v>385</v>
       </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
@@ -13369,19 +13398,19 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c t="s" r="J386" s="7">
         <v>145</v>
@@ -13402,7 +13431,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13411,13 +13440,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="I387" s="7">
         <v>177</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>282</v>
+        <v>310</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13435,22 +13464,22 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13468,7 +13497,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -13480,7 +13509,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="J389" s="7">
         <v>198</v>
@@ -13501,7 +13530,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -13513,10 +13542,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13534,7 +13563,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13546,10 +13575,10 @@
         <v>143</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13567,7 +13596,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -13579,7 +13608,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J392" s="7">
         <v>184</v>
@@ -13615,7 +13644,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
@@ -13624,7 +13653,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H394" s="8">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="I394" s="7">
         <v>145</v>
@@ -13648,22 +13677,22 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G395" s="8">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="H395" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13681,7 +13710,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
@@ -13690,7 +13719,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c t="s" r="I396" s="7">
         <v>99</v>
@@ -13714,19 +13743,19 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G397" s="8">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c t="s" r="H397" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c t="s" r="J397" s="7">
         <v>93</v>
@@ -13747,7 +13776,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -13756,10 +13785,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J398" s="7">
         <v>40</v>
@@ -13780,22 +13809,22 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13806,14 +13835,14 @@
         <v>13</v>
       </c>
       <c r="B400" s="7">
-        <v>284</v>
+        <v>160</v>
       </c>
       <c t="s" r="C400" s="7">
         <v>14</v>
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
@@ -13822,13 +13851,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>380</v>
+        <v>224</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13839,29 +13868,29 @@
         <v>13</v>
       </c>
       <c r="B401" s="7">
-        <v>285</v>
+        <v>167</v>
       </c>
       <c t="s" r="C401" s="7">
         <v>14</v>
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13894,7 +13923,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="F403" s="7">
         <v>320</v>
@@ -13906,15 +13935,15 @@
         <v>176</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
       <c t="s" r="M403" s="7">
-        <v>382</v>
+        <v>390</v>
       </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
@@ -13929,7 +13958,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="F404" s="7">
         <v>320</v>
@@ -13941,10 +13970,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13962,7 +13991,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="F405" s="7">
         <v>320</v>
@@ -13971,7 +14000,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="I405" s="7">
         <v>177</v>
@@ -13995,13 +14024,13 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="F406" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="H406" s="8">
         <v>43</v>
@@ -14010,7 +14039,7 @@
         <v>178</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -14028,7 +14057,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="F407" s="7">
         <v>320</v>
@@ -14037,13 +14066,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -14061,22 +14090,22 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="F408" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G408" s="8">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c t="s" r="H408" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -14109,7 +14138,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="F410" s="7">
         <v>320</v>
@@ -14118,13 +14147,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c t="s" r="I410" s="7">
         <v>91</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -14142,22 +14171,22 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="F411" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -14175,7 +14204,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="F412" s="7">
         <v>320</v>
@@ -14184,13 +14213,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c t="s" r="I412" s="7">
         <v>92</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14208,13 +14237,13 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="F413" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G413" s="8">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c t="s" r="H413" s="8">
         <v>21</v>
@@ -14223,7 +14252,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14241,7 +14270,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="F414" s="7">
         <v>320</v>
@@ -14250,13 +14279,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H414" s="8">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="I414" s="7">
         <v>40</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14274,19 +14303,19 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="F415" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G415" s="8">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="H415" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>380</v>
+        <v>139</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>78</v>
@@ -14322,7 +14351,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F417" s="7">
         <v>320</v>
@@ -14334,10 +14363,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14355,7 +14384,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F418" s="7">
         <v>320</v>
@@ -14370,7 +14399,7 @@
         <v>30</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14388,7 +14417,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F419" s="7">
         <v>320</v>
@@ -14397,7 +14426,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H419" s="8">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c t="s" r="I419" s="7">
         <v>92</v>
@@ -14421,19 +14450,19 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F420" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G420" s="8">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c t="s" r="H420" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J420" s="7">
         <v>25</v>
@@ -14469,7 +14498,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
@@ -14502,7 +14531,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
@@ -14514,7 +14543,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>115</v>
+        <v>301</v>
       </c>
       <c t="s" r="J423" s="7">
         <v>206</v>
@@ -14535,7 +14564,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
@@ -14568,7 +14597,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -14580,10 +14609,10 @@
         <v>77</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>286</v>
+        <v>396</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -14597,11 +14626,11 @@
         <v>8020</v>
       </c>
       <c t="s" r="C426" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
@@ -14610,13 +14639,13 @@
         <v>77</v>
       </c>
       <c t="s" r="H426" s="8">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14630,26 +14659,26 @@
         <v>8021</v>
       </c>
       <c t="s" r="C427" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G427" s="8">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c t="s" r="H427" s="8">
         <v>77</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -14682,7 +14711,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
@@ -14694,10 +14723,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -14715,7 +14744,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="F430" s="7">
         <v>321</v>
@@ -14724,13 +14753,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H430" s="8">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -14748,22 +14777,22 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="F431" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G431" s="8">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="H431" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14781,7 +14810,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="F432" s="7">
         <v>321</v>
@@ -14829,7 +14858,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="F434" s="7">
         <v>320</v>
@@ -14838,17 +14867,19 @@
         <v>43</v>
       </c>
       <c t="s" r="H434" s="8">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
-      <c r="M434" s="7"/>
+      <c t="s" r="M434" s="7">
+        <v>404</v>
+      </c>
     </row>
     <row r="435" ht="15" customHeight="1">
       <c t="s" r="A435" s="6">
@@ -14862,19 +14893,19 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="F435" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G435" s="8">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c t="s" r="H435" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J435" s="7">
         <v>223</v>
@@ -14895,7 +14926,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="F436" s="7">
         <v>320</v>
@@ -14904,13 +14935,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H436" s="8">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
@@ -14928,13 +14959,13 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="F437" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G437" s="8">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c t="s" r="H437" s="8">
         <v>43</v>
@@ -14943,7 +14974,7 @@
         <v>195</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
@@ -14976,7 +15007,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="F439" s="7">
         <v>320</v>
@@ -14985,13 +15016,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H439" s="8">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="I439" s="7">
         <v>36</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
@@ -15009,19 +15040,19 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="F440" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G440" s="8">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="H440" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c t="s" r="J440" s="7">
         <v>50</v>
@@ -15042,7 +15073,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="F441" s="7">
         <v>320</v>
@@ -15051,10 +15082,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H441" s="8">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="J441" s="7">
         <v>86</v>
@@ -15075,22 +15106,22 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="F442" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G442" s="8">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c t="s" r="H442" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
@@ -15108,7 +15139,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="F443" s="7">
         <v>320</v>
@@ -15117,13 +15148,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H443" s="8">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
@@ -15141,13 +15172,13 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="F444" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G444" s="8">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c t="s" r="H444" s="8">
         <v>21</v>
@@ -15189,7 +15220,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="F446" s="7">
         <v>321</v>
@@ -15198,18 +15229,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H446" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
-        <v>402</v>
+        <v>412</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -15224,19 +15255,19 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="F447" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G447" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H447" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I447" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J447" s="7">
         <v>171</v>
@@ -15257,7 +15288,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="F448" s="7">
         <v>321</v>
@@ -15266,13 +15297,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H448" s="8">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
@@ -15290,22 +15321,22 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="F449" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G449" s="8">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c t="s" r="H449" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
@@ -15323,7 +15354,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="F450" s="7">
         <v>321</v>
@@ -15332,10 +15363,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H450" s="8">
-        <v>138</v>
+        <v>286</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c t="s" r="J450" s="7">
         <v>41</v>
@@ -15356,22 +15387,22 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="F451" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G451" s="8">
-        <v>138</v>
+        <v>286</v>
       </c>
       <c t="s" r="H451" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -15404,7 +15435,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="F453" s="7">
         <v>321</v>
@@ -15413,10 +15444,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H453" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I453" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="J453" s="7">
         <v>145</v>
@@ -15437,22 +15468,22 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="F454" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G454" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H454" s="8">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
@@ -15470,19 +15501,19 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="F455" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G455" s="8">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c t="s" r="H455" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I455" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="J455" s="7">
         <v>195</v>
@@ -15518,7 +15549,7 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="F457" s="7">
         <v>321</v>
@@ -15533,7 +15564,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J457" s="7">
-        <v>282</v>
+        <v>310</v>
       </c>
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
@@ -15551,7 +15582,7 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="F458" s="7">
         <v>321</v>
@@ -15563,10 +15594,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I458" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="J458" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
@@ -15584,7 +15615,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="F459" s="7">
         <v>321</v>
@@ -15593,13 +15624,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H459" s="8">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c t="s" r="I459" s="7">
         <v>52</v>
       </c>
       <c t="s" r="J459" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
@@ -15617,13 +15648,13 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="F460" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G460" s="8">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c t="s" r="H460" s="8">
         <v>43</v>
@@ -15650,7 +15681,7 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="F461" s="7">
         <v>321</v>
@@ -15659,10 +15690,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H461" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I461" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="J461" s="7">
         <v>78</v>
@@ -15683,22 +15714,22 @@
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="F462" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G462" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H462" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I462" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J462" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
@@ -15731,7 +15762,7 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="F464" s="7">
         <v>321</v>
@@ -15743,15 +15774,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c t="s" r="J464" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
       <c t="s" r="M464" s="7">
-        <v>408</v>
+        <v>418</v>
       </c>
     </row>
     <row r="465" ht="15" customHeight="1">
@@ -15766,7 +15797,7 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="F465" s="7">
         <v>321</v>
@@ -15792,14 +15823,14 @@
         <v>13</v>
       </c>
       <c r="B466" s="7">
-        <v>7078</v>
+        <v>671</v>
       </c>
       <c t="s" r="C466" s="7">
         <v>14</v>
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="F466" s="7">
         <v>321</v>
@@ -15808,64 +15839,72 @@
         <v>49</v>
       </c>
       <c t="s" r="H466" s="8">
-        <v>328</v>
+        <v>176</v>
       </c>
       <c t="s" r="I466" s="7">
-        <v>289</v>
+        <v>209</v>
       </c>
       <c t="s" r="J466" s="7">
-        <v>409</v>
-      </c>
-      <c r="K466" s="7"/>
+        <v>320</v>
+      </c>
+      <c t="s" r="K466" s="7">
+        <v>310</v>
+      </c>
       <c r="L466" s="7"/>
-      <c r="M466" s="7"/>
+      <c t="s" r="M466" s="7">
+        <v>210</v>
+      </c>
     </row>
     <row r="467" ht="14.25" customHeight="1">
       <c t="s" r="A467" s="6">
         <v>13</v>
       </c>
       <c r="B467" s="7">
-        <v>7079</v>
+        <v>670</v>
       </c>
       <c t="s" r="C467" s="7">
         <v>14</v>
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="F467" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G467" s="8">
-        <v>328</v>
+        <v>176</v>
       </c>
       <c t="s" r="H467" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I467" s="7">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c t="s" r="J467" s="7">
-        <v>39</v>
-      </c>
-      <c r="K467" s="7"/>
+        <v>292</v>
+      </c>
+      <c t="s" r="K467" s="7">
+        <v>230</v>
+      </c>
       <c r="L467" s="7"/>
-      <c r="M467" s="7"/>
+      <c t="s" r="M467" s="7">
+        <v>86</v>
+      </c>
     </row>
     <row r="468" ht="14.25" customHeight="1">
       <c t="s" r="A468" s="6">
         <v>13</v>
       </c>
       <c r="B468" s="7">
-        <v>273</v>
+        <v>489</v>
       </c>
       <c t="s" r="C468" s="7">
         <v>14</v>
       </c>
       <c r="D468" s="7"/>
       <c t="s" r="E468" s="7">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="F468" s="7">
         <v>321</v>
@@ -15874,79 +15913,87 @@
         <v>49</v>
       </c>
       <c t="s" r="H468" s="8">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c t="s" r="I468" s="7">
-        <v>181</v>
+        <v>342</v>
       </c>
       <c t="s" r="J468" s="7">
-        <v>163</v>
-      </c>
-      <c r="K468" s="7"/>
+        <v>150</v>
+      </c>
+      <c t="s" r="K468" s="7">
+        <v>102</v>
+      </c>
       <c r="L468" s="7"/>
-      <c r="M468" s="7"/>
+      <c t="s" r="M468" s="7">
+        <v>304</v>
+      </c>
     </row>
     <row r="469" ht="14.25" customHeight="1">
       <c t="s" r="A469" s="6">
         <v>13</v>
       </c>
       <c r="B469" s="7">
-        <v>160</v>
+        <v>488</v>
       </c>
       <c t="s" r="C469" s="7">
         <v>14</v>
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="F469" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G469" s="8">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c t="s" r="H469" s="8">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c t="s" r="I469" s="7">
-        <v>224</v>
+        <v>181</v>
       </c>
       <c t="s" r="J469" s="7">
-        <v>302</v>
-      </c>
-      <c r="K469" s="7"/>
+        <v>121</v>
+      </c>
+      <c t="s" r="K469" s="7">
+        <v>103</v>
+      </c>
       <c r="L469" s="7"/>
-      <c r="M469" s="7"/>
+      <c t="s" r="M469" s="7">
+        <v>396</v>
+      </c>
     </row>
     <row r="470" ht="15" customHeight="1">
       <c t="s" r="A470" s="6">
         <v>13</v>
       </c>
       <c r="B470" s="7">
-        <v>167</v>
+        <v>285</v>
       </c>
       <c t="s" r="C470" s="7">
         <v>14</v>
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="F470" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G470" s="8">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c t="s" r="H470" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I470" s="7">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
@@ -15979,7 +16026,7 @@
       </c>
       <c r="D472" s="7"/>
       <c t="s" r="E472" s="7">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="F472" s="7">
         <v>320</v>
@@ -15991,7 +16038,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I472" s="7">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c t="s" r="J472" s="7">
         <v>33</v>
@@ -15999,7 +16046,7 @@
       <c r="K472" s="7"/>
       <c r="L472" s="7"/>
       <c t="s" r="M472" s="7">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="473" ht="14.25" customHeight="1">
@@ -16014,7 +16061,7 @@
       </c>
       <c r="D473" s="7"/>
       <c t="s" r="E473" s="7">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="F473" s="7">
         <v>320</v>
@@ -16047,7 +16094,7 @@
       </c>
       <c r="D474" s="7"/>
       <c t="s" r="E474" s="7">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="F474" s="7">
         <v>320</v>
@@ -16080,7 +16127,7 @@
       </c>
       <c r="D475" s="7"/>
       <c t="s" r="E475" s="7">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="F475" s="7">
         <v>320</v>
@@ -16089,7 +16136,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H475" s="8">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c t="s" r="I475" s="7">
         <v>52</v>
@@ -16113,22 +16160,22 @@
       </c>
       <c r="D476" s="7"/>
       <c t="s" r="E476" s="7">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="F476" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G476" s="8">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c t="s" r="H476" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I476" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="J476" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K476" s="7"/>
       <c r="L476" s="7"/>
@@ -16146,7 +16193,7 @@
       </c>
       <c r="D477" s="7"/>
       <c t="s" r="E477" s="7">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="F477" s="7">
         <v>320</v>
@@ -16155,13 +16202,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H477" s="8">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="I477" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="J477" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K477" s="7"/>
       <c r="L477" s="7"/>
@@ -16179,22 +16226,22 @@
       </c>
       <c r="D478" s="7"/>
       <c t="s" r="E478" s="7">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="F478" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G478" s="8">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="H478" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I478" s="7">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c t="s" r="J478" s="7">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="K478" s="7"/>
       <c r="L478" s="7"/>
@@ -16227,7 +16274,7 @@
       </c>
       <c r="D480" s="7"/>
       <c t="s" r="E480" s="7">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="F480" s="7">
         <v>321</v>
@@ -16239,7 +16286,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I480" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J480" s="7">
         <v>69</v>
@@ -16260,7 +16307,7 @@
       </c>
       <c r="D481" s="7"/>
       <c t="s" r="E481" s="7">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="F481" s="7">
         <v>321</v>
@@ -16269,10 +16316,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H481" s="8">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="I481" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="J481" s="7">
         <v>40</v>
@@ -16293,19 +16340,19 @@
       </c>
       <c r="D482" s="7"/>
       <c t="s" r="E482" s="7">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="F482" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G482" s="8">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="H482" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I482" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J482" s="7">
         <v>191</v>
@@ -16326,7 +16373,7 @@
       </c>
       <c r="D483" s="7"/>
       <c t="s" r="E483" s="7">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="F483" s="7">
         <v>321</v>
@@ -16341,7 +16388,7 @@
         <v>217</v>
       </c>
       <c t="s" r="J483" s="7">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="K483" s="7"/>
       <c r="L483" s="7"/>
@@ -16374,7 +16421,7 @@
       </c>
       <c r="D485" s="7"/>
       <c t="s" r="E485" s="7">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="F485" s="7">
         <v>321</v>
@@ -16383,13 +16430,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H485" s="8">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="I485" s="7">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c t="s" r="J485" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K485" s="7"/>
       <c r="L485" s="7"/>
@@ -16407,22 +16454,22 @@
       </c>
       <c r="D486" s="7"/>
       <c t="s" r="E486" s="7">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="F486" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G486" s="8">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="H486" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I486" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J486" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K486" s="7"/>
       <c r="L486" s="7"/>
@@ -16440,7 +16487,7 @@
       </c>
       <c r="D487" s="7"/>
       <c t="s" r="E487" s="7">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="F487" s="7">
         <v>321</v>
@@ -16449,13 +16496,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H487" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I487" s="7">
         <v>94</v>
       </c>
       <c t="s" r="J487" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K487" s="7"/>
       <c r="L487" s="7"/>
@@ -16473,22 +16520,22 @@
       </c>
       <c r="D488" s="7"/>
       <c t="s" r="E488" s="7">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="F488" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G488" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H488" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I488" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J488" s="7">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="K488" s="7"/>
       <c r="L488" s="7"/>
@@ -16521,7 +16568,7 @@
       </c>
       <c r="D490" s="7"/>
       <c t="s" r="E490" s="7">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="F490" s="7">
         <v>320</v>
@@ -16536,7 +16583,7 @@
         <v>145</v>
       </c>
       <c t="s" r="J490" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K490" s="7"/>
       <c r="L490" s="7"/>
@@ -16554,7 +16601,7 @@
       </c>
       <c r="D491" s="7"/>
       <c t="s" r="E491" s="7">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="F491" s="7">
         <v>320</v>
@@ -16569,7 +16616,7 @@
         <v>177</v>
       </c>
       <c t="s" r="J491" s="7">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="K491" s="7"/>
       <c r="L491" s="7"/>
@@ -16587,7 +16634,7 @@
       </c>
       <c r="D492" s="7"/>
       <c t="s" r="E492" s="7">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="F492" s="7">
         <v>320</v>
@@ -16602,7 +16649,7 @@
         <v>205</v>
       </c>
       <c t="s" r="J492" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K492" s="7"/>
       <c r="L492" s="7"/>
@@ -16620,7 +16667,7 @@
       </c>
       <c r="D493" s="7"/>
       <c t="s" r="E493" s="7">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="F493" s="7">
         <v>320</v>
@@ -16632,7 +16679,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I493" s="7">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c t="s" r="J493" s="7">
         <v>39</v>
@@ -16653,7 +16700,7 @@
       </c>
       <c r="D494" s="7"/>
       <c t="s" r="E494" s="7">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="F494" s="7">
         <v>320</v>
@@ -16665,10 +16712,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I494" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="J494" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="K494" s="7"/>
       <c r="L494" s="7"/>
@@ -16686,7 +16733,7 @@
       </c>
       <c r="D495" s="7"/>
       <c t="s" r="E495" s="7">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="F495" s="7">
         <v>320</v>
@@ -16701,7 +16748,7 @@
         <v>182</v>
       </c>
       <c t="s" r="J495" s="7">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="K495" s="7"/>
       <c r="L495" s="7"/>
@@ -16734,22 +16781,22 @@
       </c>
       <c r="D497" s="7"/>
       <c t="s" r="E497" s="7">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="F497" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G497" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H497" s="8">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c t="s" r="I497" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J497" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K497" s="7"/>
       <c r="L497" s="7"/>
@@ -16767,19 +16814,19 @@
       </c>
       <c r="D498" s="7"/>
       <c t="s" r="E498" s="7">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="F498" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G498" s="8">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c t="s" r="H498" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I498" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J498" s="7">
         <v>33</v>
@@ -16815,29 +16862,29 @@
       </c>
       <c r="D500" s="7"/>
       <c t="s" r="E500" s="7">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="F500" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G500" s="8">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c t="s" r="H500" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I500" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J500" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="K500" s="7">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="L500" s="7"/>
       <c t="s" r="M500" s="7">
-        <v>137</v>
+        <v>100</v>
       </c>
     </row>
     <row r="501" ht="14.25" customHeight="1">
@@ -16852,19 +16899,19 @@
       </c>
       <c r="D501" s="7"/>
       <c t="s" r="E501" s="7">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="F501" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G501" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H501" s="8">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c t="s" r="I501" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="J501" s="7">
         <v>18</v>
@@ -16900,22 +16947,22 @@
       </c>
       <c r="D503" s="7"/>
       <c t="s" r="E503" s="7">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="F503" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G503" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H503" s="8">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c t="s" r="I503" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J503" s="7">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="K503" s="7"/>
       <c r="L503" s="7"/>
@@ -16933,22 +16980,22 @@
       </c>
       <c r="D504" s="7"/>
       <c t="s" r="E504" s="7">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="F504" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G504" s="8">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c t="s" r="H504" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I504" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c t="s" r="J504" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K504" s="7"/>
       <c r="L504" s="7"/>
@@ -16981,7 +17028,7 @@
       </c>
       <c r="D506" s="7"/>
       <c t="s" r="E506" s="7">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="F506" s="7">
         <v>330</v>
@@ -16990,10 +17037,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H506" s="8">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c t="s" r="I506" s="7">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c t="s" r="J506" s="7">
         <v>36</v>
@@ -17033,7 +17080,7 @@
       </c>
       <c r="D508" s="7"/>
       <c t="s" r="E508" s="7">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="F508" s="7">
         <v>330</v>
@@ -17048,14 +17095,14 @@
         <v>177</v>
       </c>
       <c t="s" r="J508" s="7">
-        <v>282</v>
+        <v>310</v>
       </c>
       <c t="s" r="K508" s="7">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="L508" s="7"/>
       <c t="s" r="M508" s="7">
-        <v>289</v>
+        <v>284</v>
       </c>
     </row>
     <row r="509" ht="14.25" customHeight="1">
@@ -17070,7 +17117,7 @@
       </c>
       <c r="D509" s="7"/>
       <c t="s" r="E509" s="7">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="F509" s="7">
         <v>330</v>
@@ -17079,13 +17126,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H509" s="8">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c t="s" r="I509" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="J509" s="7">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="K509" s="7"/>
       <c r="L509" s="7"/>
@@ -17118,7 +17165,7 @@
       </c>
       <c r="D511" s="7"/>
       <c t="s" r="E511" s="7">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="F511" s="7">
         <v>330</v>
@@ -17130,7 +17177,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I511" s="7">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c t="s" r="J511" s="7">
         <v>145</v>
@@ -17144,14 +17191,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B512" s="7">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c t="s" r="C512" s="7">
         <v>14</v>
       </c>
       <c r="D512" s="7"/>
       <c t="s" r="E512" s="7">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="F512" s="7">
         <v>330</v>
@@ -17160,7 +17207,7 @@
         <v>77</v>
       </c>
       <c t="s" r="H512" s="8">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c t="s" r="I512" s="7">
         <v>22</v>
@@ -17188,19 +17235,19 @@
       </c>
       <c r="D513" s="7"/>
       <c t="s" r="E513" s="7">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="F513" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G513" s="8">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c t="s" r="H513" s="8">
         <v>77</v>
       </c>
       <c t="s" r="I513" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J513" s="7">
         <v>201</v>
@@ -17236,7 +17283,7 @@
       </c>
       <c r="D515" s="7"/>
       <c t="s" r="E515" s="7">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="F515" s="7">
         <v>330</v>
@@ -17245,13 +17292,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H515" s="8">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c t="s" r="I515" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J515" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K515" s="7"/>
       <c r="L515" s="7"/>
@@ -17269,13 +17316,13 @@
       </c>
       <c r="D516" s="7"/>
       <c t="s" r="E516" s="7">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="F516" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G516" s="8">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c t="s" r="H516" s="8">
         <v>21</v>
@@ -17284,7 +17331,7 @@
         <v>27</v>
       </c>
       <c t="s" r="J516" s="7">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="K516" s="7"/>
       <c r="L516" s="7"/>
@@ -17292,7 +17339,7 @@
     </row>
     <row r="517" ht="15.75" customHeight="1">
       <c t="s" r="A517" s="9">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B517" s="9"/>
       <c r="C517" s="9"/>
@@ -17312,7 +17359,7 @@
     <row r="518" ht="65.25" customHeight="1"/>
     <row r="519" ht="16.5" customHeight="1">
       <c t="s" r="A519" s="10">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="B519" s="10"/>
       <c r="C519" s="10"/>
@@ -17325,7 +17372,7 @@
       <c r="J519" s="10"/>
       <c r="K519" s="10"/>
       <c t="s" r="L519" s="11">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="M519" s="11"/>
       <c r="N519" s="11"/>

--- a/Data/FlightPlan/FPL_11AUG26.xlsx
+++ b/Data/FlightPlan/FPL_11AUG26.xlsx
@@ -575,7 +575,7 @@
     <t>20:45</t>
   </si>
   <si>
-    <t>01:02</t>
+    <t>00:44</t>
   </si>
   <si>
     <t>05:35</t>
@@ -1217,6 +1217,9 @@
     <t>22:15</t>
   </si>
   <si>
+    <t>00:25</t>
+  </si>
+  <si>
     <t>VN-A635</t>
   </si>
   <si>
@@ -1391,6 +1394,9 @@
     <t>23:17</t>
   </si>
   <si>
+    <t>01:50</t>
+  </si>
+  <si>
     <t>VN-A642</t>
   </si>
   <si>
@@ -1433,9 +1439,6 @@
     <t>22:00</t>
   </si>
   <si>
-    <t>00:55</t>
-  </si>
-  <si>
     <t>VN-A644</t>
   </si>
   <si>
@@ -1895,7 +1898,7 @@
     <t>17:24</t>
   </si>
   <si>
-    <t>00:25</t>
+    <t>23:38</t>
   </si>
   <si>
     <t>VN-A683</t>
@@ -1988,7 +1991,7 @@
     <t>04:30</t>
   </si>
   <si>
-    <t>05:01</t>
+    <t>05:10</t>
   </si>
   <si>
     <t>VN-A699</t>
@@ -2066,6 +2069,9 @@
     <t>16:39</t>
   </si>
   <si>
+    <t>08:51</t>
+  </si>
+  <si>
     <t>VN-A820</t>
   </si>
   <si>
@@ -2075,7 +2081,7 @@
     <t>Total Record(s): 434</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 11, 2026 22:22</t>
+    <t xml:space="preserve">Generated on  Aug 11, 2026 22:33</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -9281,7 +9287,9 @@
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
-      <c r="M217" s="7"/>
+      <c t="s" r="M217" s="7">
+        <v>402</v>
+      </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
       <c r="A218" s="6"/>
@@ -9310,7 +9318,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -9325,12 +9333,12 @@
         <v>165</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -9345,7 +9353,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -9365,7 +9373,7 @@
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -9380,7 +9388,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -9400,7 +9408,7 @@
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -9415,7 +9423,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -9435,7 +9443,7 @@
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -9450,7 +9458,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -9459,10 +9467,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>309</v>
@@ -9470,7 +9478,7 @@
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -9485,13 +9493,13 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>21</v>
@@ -9522,7 +9530,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -9544,7 +9552,7 @@
       </c>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -9559,7 +9567,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -9581,7 +9589,7 @@
       </c>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -9611,7 +9619,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -9620,10 +9628,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c t="s" r="J228" s="7">
         <v>53</v>
@@ -9646,13 +9654,13 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>21</v>
@@ -9666,7 +9674,7 @@
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -9681,7 +9689,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -9693,7 +9701,7 @@
         <v>371</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>236</v>
@@ -9701,7 +9709,7 @@
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -9716,7 +9724,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -9728,7 +9736,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c t="s" r="J231" s="7">
         <v>198</v>
@@ -9736,7 +9744,7 @@
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
@@ -9751,7 +9759,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9766,12 +9774,12 @@
         <v>131</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -9786,7 +9794,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9801,12 +9809,12 @@
         <v>374</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -9821,7 +9829,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9836,7 +9844,7 @@
         <v>385</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -9869,7 +9877,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9878,7 +9886,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c t="s" r="I236" s="7">
         <v>194</v>
@@ -9889,7 +9897,7 @@
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9904,22 +9912,22 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -9939,7 +9947,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9951,7 +9959,7 @@
         <v>91</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c t="s" r="J238" s="7">
         <v>73</v>
@@ -9959,7 +9967,7 @@
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
       <c t="s" r="M238" s="7">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="239" ht="14.25" customHeight="1">
@@ -9974,7 +9982,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9994,7 +10002,7 @@
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -10009,7 +10017,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -10029,7 +10037,7 @@
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
@@ -10044,7 +10052,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -10092,7 +10100,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -10107,12 +10115,12 @@
         <v>67</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
@@ -10127,7 +10135,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -10147,7 +10155,7 @@
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -10162,7 +10170,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -10182,7 +10190,7 @@
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -10197,7 +10205,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -10217,7 +10225,7 @@
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c t="s" r="M246" s="7">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
@@ -10232,7 +10240,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -10252,7 +10260,7 @@
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -10267,7 +10275,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -10282,12 +10290,12 @@
         <v>374</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -10317,7 +10325,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -10329,15 +10337,15 @@
         <v>143</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c t="s" r="M250" s="7">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
@@ -10352,7 +10360,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -10372,7 +10380,7 @@
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -10387,7 +10395,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -10407,7 +10415,7 @@
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
       <c t="s" r="M252" s="7">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
@@ -10422,7 +10430,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -10442,7 +10450,7 @@
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -10457,7 +10465,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -10469,7 +10477,7 @@
         <v>301</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c t="s" r="J254" s="7">
         <v>128</v>
@@ -10477,7 +10485,7 @@
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -10492,7 +10500,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -10512,7 +10520,7 @@
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -10527,7 +10535,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -10564,7 +10572,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -10579,14 +10587,14 @@
         <v>374</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c t="s" r="K257" s="7">
         <v>159</v>
       </c>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -10601,7 +10609,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -10613,10 +10621,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -10649,7 +10657,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -10669,7 +10677,7 @@
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -10684,7 +10692,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -10696,7 +10704,7 @@
         <v>232</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c t="s" r="J261" s="7">
         <v>244</v>
@@ -10704,7 +10712,7 @@
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c t="s" r="M261" s="7">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
@@ -10719,7 +10727,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -10754,7 +10762,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -10789,7 +10797,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -10809,7 +10817,7 @@
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -10824,7 +10832,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -10839,7 +10847,7 @@
         <v>131</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -10852,67 +10860,71 @@
         <v>13</v>
       </c>
       <c r="B266" s="7">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c t="s" r="C266" s="7">
         <v>14</v>
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
+        <v>21</v>
+      </c>
+      <c t="s" r="H266" s="8">
         <v>91</v>
       </c>
-      <c t="s" r="H266" s="8">
-        <v>21</v>
-      </c>
       <c t="s" r="I266" s="7">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>353</v>
+        <v>298</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
-      <c r="M266" s="7"/>
+      <c t="s" r="M266" s="7">
+        <v>460</v>
+      </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
       <c t="s" r="A267" s="6">
         <v>13</v>
       </c>
       <c r="B267" s="7">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c t="s" r="C267" s="7">
         <v>14</v>
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
+        <v>91</v>
+      </c>
+      <c t="s" r="H267" s="8">
         <v>21</v>
       </c>
-      <c t="s" r="H267" s="8">
-        <v>91</v>
-      </c>
       <c t="s" r="I267" s="7">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>298</v>
-      </c>
-      <c r="K267" s="7"/>
+        <v>353</v>
+      </c>
+      <c t="s" r="K267" s="7">
+        <v>29</v>
+      </c>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -10942,7 +10954,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -10962,7 +10974,7 @@
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10977,7 +10989,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -11012,7 +11024,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -11027,12 +11039,12 @@
         <v>81</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -11047,7 +11059,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -11067,7 +11079,7 @@
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -11082,7 +11094,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -11097,12 +11109,12 @@
         <v>216</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -11117,7 +11129,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -11137,7 +11149,7 @@
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -11167,7 +11179,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -11202,7 +11214,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -11222,7 +11234,7 @@
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
       <c t="s" r="M277" s="7">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
@@ -11237,7 +11249,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -11257,7 +11269,7 @@
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -11272,7 +11284,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -11287,12 +11299,12 @@
         <v>41</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -11307,7 +11319,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -11327,7 +11339,7 @@
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -11342,7 +11354,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -11379,7 +11391,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -11394,14 +11406,14 @@
         <v>64</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c t="s" r="K282" s="7">
-        <v>474</v>
+        <v>175</v>
       </c>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>357</v>
+        <v>402</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -11431,7 +11443,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -11451,7 +11463,7 @@
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -11466,7 +11478,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -11501,7 +11513,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -11521,7 +11533,7 @@
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -11536,7 +11548,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -11556,7 +11568,7 @@
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -11571,7 +11583,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -11583,7 +11595,7 @@
         <v>91</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>385</v>
@@ -11591,7 +11603,7 @@
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -11621,7 +11633,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -11633,7 +11645,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c t="s" r="J290" s="7">
         <v>33</v>
@@ -11641,7 +11653,7 @@
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -11656,7 +11668,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -11676,7 +11688,7 @@
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -11691,7 +11703,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -11711,7 +11723,7 @@
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -11726,7 +11738,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -11746,7 +11758,7 @@
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -11761,7 +11773,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -11781,7 +11793,7 @@
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -11796,7 +11808,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
@@ -11805,13 +11817,13 @@
         <v>50</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c t="s" r="I295" s="7">
         <v>175</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -11844,7 +11856,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
@@ -11853,10 +11865,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c t="s" r="J297" s="7">
         <v>183</v>
@@ -11864,7 +11876,7 @@
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -11879,13 +11891,13 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>21</v>
@@ -11894,12 +11906,12 @@
         <v>226</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -11914,7 +11926,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -11923,7 +11935,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c t="s" r="I299" s="7">
         <v>73</v>
@@ -11934,7 +11946,7 @@
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
       <c t="s" r="M299" s="7">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1">
@@ -11949,22 +11961,22 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -11997,7 +12009,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -12009,15 +12021,15 @@
         <v>50</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
       <c t="s" r="M302" s="7">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="303" ht="14.25" customHeight="1">
@@ -12032,7 +12044,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -12052,7 +12064,7 @@
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
       <c t="s" r="M303" s="7">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="304" ht="14.25" customHeight="1">
@@ -12067,7 +12079,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -12082,12 +12094,12 @@
         <v>140</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -12102,7 +12114,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -12137,7 +12149,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -12146,7 +12158,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c t="s" r="I306" s="7">
         <v>215</v>
@@ -12157,7 +12169,7 @@
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -12172,13 +12184,13 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>21</v>
@@ -12192,7 +12204,7 @@
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -12207,7 +12219,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -12244,7 +12256,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -12266,7 +12278,7 @@
       </c>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -12296,7 +12308,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -12316,7 +12328,7 @@
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -12331,7 +12343,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -12340,13 +12352,13 @@
         <v>50</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c t="s" r="I312" s="7">
         <v>172</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -12366,13 +12378,13 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c t="s" r="H313" s="8">
         <v>50</v>
@@ -12386,7 +12398,7 @@
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -12401,7 +12413,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -12416,7 +12428,7 @@
         <v>353</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -12449,7 +12461,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -12461,7 +12473,7 @@
         <v>91</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>19</v>
@@ -12469,7 +12481,7 @@
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -12484,7 +12496,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -12504,7 +12516,7 @@
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -12519,7 +12531,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -12554,7 +12566,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -12569,12 +12581,12 @@
         <v>42</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -12589,7 +12601,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -12604,12 +12616,12 @@
         <v>83</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -12624,7 +12636,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
@@ -12659,7 +12671,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -12671,17 +12683,17 @@
         <v>91</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c t="s" r="J322" s="7">
         <v>206</v>
       </c>
       <c t="s" r="K322" s="7">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -12696,7 +12708,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
@@ -12711,7 +12723,7 @@
         <v>312</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c t="s" r="K323" s="7">
         <v>177</v>
@@ -12748,7 +12760,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -12760,15 +12772,15 @@
         <v>50</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -12783,7 +12795,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -12803,7 +12815,7 @@
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
       <c t="s" r="M326" s="7">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
@@ -12818,7 +12830,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -12853,7 +12865,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -12868,14 +12880,14 @@
         <v>102</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c t="s" r="K328" s="7">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -12890,7 +12902,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -12902,17 +12914,17 @@
         <v>50</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c t="s" r="K329" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -12927,7 +12939,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -12942,12 +12954,12 @@
         <v>159</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -12962,7 +12974,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -12977,14 +12989,14 @@
         <v>186</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c t="s" r="K331" s="7">
         <v>177</v>
       </c>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -13014,7 +13026,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -13026,7 +13038,7 @@
         <v>91</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c t="s" r="J333" s="7">
         <v>194</v>
@@ -13034,7 +13046,7 @@
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -13049,7 +13061,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -13071,7 +13083,7 @@
       </c>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1">
@@ -13086,7 +13098,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -13108,7 +13120,7 @@
       </c>
       <c r="L335" s="7"/>
       <c t="s" r="M335" s="7">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
@@ -13123,7 +13135,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -13145,7 +13157,7 @@
       </c>
       <c r="L336" s="7"/>
       <c t="s" r="M336" s="7">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
@@ -13160,7 +13172,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
@@ -13178,7 +13190,7 @@
         <v>131</v>
       </c>
       <c t="s" r="K337" s="7">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
@@ -13197,7 +13209,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -13215,11 +13227,11 @@
         <v>47</v>
       </c>
       <c t="s" r="K338" s="7">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -13234,7 +13246,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -13256,7 +13268,7 @@
       </c>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -13271,7 +13283,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -13286,7 +13298,7 @@
         <v>187</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c t="s" r="K340" s="7">
         <v>385</v>
@@ -13323,7 +13335,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
@@ -13345,7 +13357,7 @@
       </c>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -13360,7 +13372,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -13382,7 +13394,7 @@
       </c>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -13412,7 +13424,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -13424,7 +13436,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>53</v>
@@ -13432,7 +13444,7 @@
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -13447,7 +13459,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -13467,7 +13479,7 @@
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -13482,7 +13494,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -13502,7 +13514,7 @@
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c t="s" r="M347" s="7">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
@@ -13517,7 +13529,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -13529,7 +13541,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c t="s" r="J348" s="7">
         <v>216</v>
@@ -13537,7 +13549,7 @@
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -13552,7 +13564,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -13602,7 +13614,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -13611,7 +13623,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c t="s" r="I351" s="7">
         <v>260</v>
@@ -13622,7 +13634,7 @@
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -13637,13 +13649,13 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>21</v>
@@ -13652,12 +13664,12 @@
         <v>275</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -13672,7 +13684,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -13687,12 +13699,12 @@
         <v>141</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -13707,7 +13719,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -13727,7 +13739,7 @@
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -13742,7 +13754,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -13777,7 +13789,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -13825,7 +13837,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -13860,7 +13872,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
@@ -13895,7 +13907,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
@@ -13910,12 +13922,12 @@
         <v>41</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13930,7 +13942,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
@@ -13939,7 +13951,7 @@
         <v>50</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c t="s" r="I361" s="7">
         <v>141</v>
@@ -13948,11 +13960,11 @@
         <v>250</v>
       </c>
       <c t="s" r="K361" s="7">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -13967,19 +13979,19 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c t="s" r="H362" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c t="s" r="J362" s="7">
         <v>205</v>
@@ -13989,7 +14001,7 @@
       </c>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -14004,7 +14016,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
@@ -14013,7 +14025,7 @@
         <v>50</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c t="s" r="I363" s="7">
         <v>309</v>
@@ -14026,7 +14038,7 @@
       </c>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -14041,13 +14053,13 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>50</v>
@@ -14093,7 +14105,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -14128,7 +14140,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -14140,7 +14152,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>194</v>
@@ -14148,7 +14160,7 @@
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -14163,7 +14175,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -14172,7 +14184,7 @@
         <v>50</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c t="s" r="I368" s="7">
         <v>115</v>
@@ -14183,7 +14195,7 @@
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -14198,13 +14210,13 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c t="s" r="H369" s="8">
         <v>50</v>
@@ -14233,7 +14245,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -14242,10 +14254,10 @@
         <v>50</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c t="s" r="J370" s="7">
         <v>81</v>
@@ -14253,7 +14265,7 @@
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -14268,13 +14280,13 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c t="s" r="H371" s="8">
         <v>50</v>
@@ -14303,7 +14315,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -14323,7 +14335,7 @@
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
       <c t="s" r="M372" s="7">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
@@ -14338,7 +14350,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -14347,7 +14359,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c t="s" r="I373" s="7">
         <v>384</v>
@@ -14360,7 +14372,7 @@
       </c>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -14375,22 +14387,22 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c t="s" r="H374" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c t="s" r="K374" s="7">
         <v>35</v>
@@ -14427,7 +14439,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -14439,15 +14451,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -14462,7 +14474,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -14477,12 +14489,12 @@
         <v>70</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -14497,7 +14509,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -14517,7 +14529,7 @@
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -14532,7 +14544,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -14552,7 +14564,7 @@
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -14567,7 +14579,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
@@ -14587,7 +14599,7 @@
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
       <c t="s" r="M380" s="7">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
@@ -14602,7 +14614,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
@@ -14622,7 +14634,7 @@
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -14637,7 +14649,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -14687,13 +14699,13 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>50</v>
@@ -14707,7 +14719,7 @@
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -14722,7 +14734,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
@@ -14742,7 +14754,7 @@
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
       <c t="s" r="M385" s="7">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
@@ -14757,7 +14769,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
@@ -14772,12 +14784,12 @@
         <v>251</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
       <c t="s" r="M386" s="7">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
@@ -14807,7 +14819,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
@@ -14827,7 +14839,7 @@
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -14842,7 +14854,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -14862,7 +14874,7 @@
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -14877,7 +14889,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
@@ -14897,7 +14909,7 @@
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -14912,7 +14924,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -14927,12 +14939,12 @@
         <v>140</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -14947,7 +14959,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -14956,10 +14968,10 @@
         <v>50</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c t="s" r="J392" s="7">
         <v>309</v>
@@ -14967,7 +14979,7 @@
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -14982,13 +14994,13 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>50</v>
@@ -15002,7 +15014,7 @@
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
       <c t="s" r="M393" s="7">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
@@ -15032,7 +15044,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -15041,10 +15053,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>348</v>
@@ -15052,7 +15064,7 @@
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -15067,19 +15079,19 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c t="s" r="J396" s="7">
         <v>194</v>
@@ -15102,7 +15114,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -15111,13 +15123,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c t="s" r="I397" s="7">
         <v>233</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -15137,13 +15149,13 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c t="s" r="H398" s="8">
         <v>21</v>
@@ -15152,7 +15164,7 @@
         <v>389</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -15172,7 +15184,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -15181,7 +15193,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c t="s" r="I399" s="7">
         <v>199</v>
@@ -15192,7 +15204,7 @@
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
       <c t="s" r="M399" s="7">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="400" ht="15" customHeight="1">
@@ -15207,13 +15219,13 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c t="s" r="H400" s="8">
         <v>17</v>
@@ -15235,14 +15247,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B401" s="7">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c t="s" r="C401" s="7">
         <v>14</v>
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -15290,7 +15302,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F403" s="7">
         <v>320</v>
@@ -15299,7 +15311,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c t="s" r="I403" s="7">
         <v>194</v>
@@ -15310,7 +15322,7 @@
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
       <c t="s" r="M403" s="7">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
@@ -15325,13 +15337,13 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F404" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>21</v>
@@ -15345,7 +15357,7 @@
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -15360,7 +15372,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F405" s="7">
         <v>320</v>
@@ -15369,7 +15381,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c t="s" r="I405" s="7">
         <v>126</v>
@@ -15380,7 +15392,7 @@
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -15395,13 +15407,13 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F406" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c t="s" r="H406" s="8">
         <v>21</v>
@@ -15430,7 +15442,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F407" s="7">
         <v>320</v>
@@ -15439,10 +15451,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c t="s" r="J407" s="7">
         <v>280</v>
@@ -15450,7 +15462,7 @@
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -15465,13 +15477,13 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F408" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G408" s="8">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c t="s" r="H408" s="8">
         <v>21</v>
@@ -15513,7 +15525,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F410" s="7">
         <v>320</v>
@@ -15525,7 +15537,7 @@
         <v>232</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c t="s" r="J410" s="7">
         <v>151</v>
@@ -15533,7 +15545,7 @@
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -15548,7 +15560,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F411" s="7">
         <v>320</v>
@@ -15560,7 +15572,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>168</v>
@@ -15583,7 +15595,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F412" s="7">
         <v>320</v>
@@ -15592,7 +15604,7 @@
         <v>50</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c t="s" r="I412" s="7">
         <v>233</v>
@@ -15603,7 +15615,7 @@
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -15618,13 +15630,13 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F413" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G413" s="8">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c t="s" r="H413" s="8">
         <v>50</v>
@@ -15638,7 +15650,7 @@
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -15653,7 +15665,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F414" s="7">
         <v>320</v>
@@ -15662,10 +15674,10 @@
         <v>50</v>
       </c>
       <c t="s" r="H414" s="8">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c t="s" r="J414" s="7">
         <v>157</v>
@@ -15673,7 +15685,7 @@
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
       <c t="s" r="M414" s="7">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="415" ht="15" customHeight="1">
@@ -15688,13 +15700,13 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F415" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G415" s="8">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c t="s" r="H415" s="8">
         <v>50</v>
@@ -15708,7 +15720,7 @@
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
       <c t="s" r="M415" s="7">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -15738,7 +15750,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -15773,7 +15785,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -15788,7 +15800,7 @@
         <v>172</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -15808,7 +15820,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -15828,7 +15840,7 @@
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
       <c t="s" r="M419" s="7">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="420" ht="15" customHeight="1">
@@ -15843,7 +15855,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -15891,7 +15903,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F422" s="7">
         <v>320</v>
@@ -15900,7 +15912,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H422" s="8">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c t="s" r="I422" s="7">
         <v>115</v>
@@ -15926,13 +15938,13 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F423" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>21</v>
@@ -15946,7 +15958,7 @@
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
       <c t="s" r="M423" s="7">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
@@ -15961,7 +15973,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F424" s="7">
         <v>320</v>
@@ -15970,13 +15982,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H424" s="8">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c t="s" r="I424" s="7">
         <v>117</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -15996,13 +16008,13 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F425" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G425" s="8">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c t="s" r="H425" s="8">
         <v>21</v>
@@ -16011,7 +16023,7 @@
         <v>61</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -16031,7 +16043,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F426" s="7">
         <v>320</v>
@@ -16066,7 +16078,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F427" s="7">
         <v>320</v>
@@ -16088,7 +16100,7 @@
       </c>
       <c r="L427" s="7"/>
       <c t="s" r="M427" s="7">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="428" ht="14.25" customHeight="1">
@@ -16118,7 +16130,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F429" s="7">
         <v>320</v>
@@ -16133,12 +16145,12 @@
         <v>166</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
       <c t="s" r="M429" s="7">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="430" ht="15" customHeight="1">
@@ -16153,7 +16165,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F430" s="7">
         <v>320</v>
@@ -16173,7 +16185,7 @@
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
       <c t="s" r="M430" s="7">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="431" ht="14.25" customHeight="1">
@@ -16188,7 +16200,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F431" s="7">
         <v>320</v>
@@ -16197,7 +16209,7 @@
         <v>50</v>
       </c>
       <c t="s" r="H431" s="8">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c t="s" r="I431" s="7">
         <v>117</v>
@@ -16223,13 +16235,13 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F432" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G432" s="8">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c t="s" r="H432" s="8">
         <v>50</v>
@@ -16273,7 +16285,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
@@ -16293,7 +16305,7 @@
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
       <c t="s" r="M434" s="7">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="435" ht="15" customHeight="1">
@@ -16308,7 +16320,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
@@ -16320,7 +16332,7 @@
         <v>91</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c t="s" r="J435" s="7">
         <v>269</v>
@@ -16328,7 +16340,7 @@
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
       <c t="s" r="M435" s="7">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="436" ht="14.25" customHeight="1">
@@ -16343,7 +16355,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
@@ -16358,12 +16370,12 @@
         <v>42</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
       <c t="s" r="M436" s="7">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
@@ -16378,7 +16390,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F437" s="7">
         <v>321</v>
@@ -16413,7 +16425,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F438" s="7">
         <v>321</v>
@@ -16422,7 +16434,7 @@
         <v>91</v>
       </c>
       <c t="s" r="H438" s="8">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c t="s" r="I438" s="7">
         <v>175</v>
@@ -16446,13 +16458,13 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G439" s="8">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c t="s" r="H439" s="8">
         <v>91</v>
@@ -16461,7 +16473,7 @@
         <v>316</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
@@ -16494,7 +16506,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F441" s="7">
         <v>321</v>
@@ -16509,12 +16521,12 @@
         <v>348</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
       <c t="s" r="M441" s="7">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="442" ht="14.25" customHeight="1">
@@ -16529,7 +16541,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F442" s="7">
         <v>321</v>
@@ -16541,7 +16553,7 @@
         <v>350</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c t="s" r="J442" s="7">
         <v>131</v>
@@ -16549,7 +16561,7 @@
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
       <c t="s" r="M442" s="7">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="443" ht="14.25" customHeight="1">
@@ -16564,7 +16576,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F443" s="7">
         <v>321</v>
@@ -16584,7 +16596,7 @@
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
       <c t="s" r="M443" s="7">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="444" ht="14.25" customHeight="1">
@@ -16599,7 +16611,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F444" s="7">
         <v>321</v>
@@ -16647,7 +16659,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F446" s="7">
         <v>320</v>
@@ -16656,7 +16668,7 @@
         <v>50</v>
       </c>
       <c t="s" r="H446" s="8">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c t="s" r="I446" s="7">
         <v>178</v>
@@ -16667,7 +16679,7 @@
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -16682,13 +16694,13 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F447" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G447" s="8">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c t="s" r="H447" s="8">
         <v>50</v>
@@ -16702,7 +16714,7 @@
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
       <c t="s" r="M447" s="7">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="448" ht="14.25" customHeight="1">
@@ -16717,7 +16729,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F448" s="7">
         <v>320</v>
@@ -16726,18 +16738,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H448" s="8">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c t="s" r="I448" s="7">
         <v>27</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
       <c t="s" r="M448" s="7">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="449" ht="14.25" customHeight="1">
@@ -16752,13 +16764,13 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F449" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G449" s="8">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c t="s" r="H449" s="8">
         <v>50</v>
@@ -16767,7 +16779,7 @@
         <v>258</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
@@ -16800,7 +16812,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F451" s="7">
         <v>320</v>
@@ -16815,12 +16827,12 @@
         <v>39</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
       <c t="s" r="M451" s="7">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="452" ht="14.25" customHeight="1">
@@ -16835,7 +16847,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F452" s="7">
         <v>320</v>
@@ -16847,7 +16859,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c t="s" r="J452" s="7">
         <v>41</v>
@@ -16855,7 +16867,7 @@
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
       <c t="s" r="M452" s="7">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="453" ht="14.25" customHeight="1">
@@ -16870,7 +16882,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F453" s="7">
         <v>320</v>
@@ -16879,7 +16891,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H453" s="8">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c t="s" r="I453" s="7">
         <v>140</v>
@@ -16890,7 +16902,7 @@
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
       <c t="s" r="M453" s="7">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="454" ht="14.25" customHeight="1">
@@ -16905,19 +16917,19 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F454" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G454" s="8">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c t="s" r="H454" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c t="s" r="J454" s="7">
         <v>201</v>
@@ -16925,7 +16937,7 @@
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
       <c t="s" r="M454" s="7">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="455" ht="15" customHeight="1">
@@ -16940,7 +16952,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F455" s="7">
         <v>320</v>
@@ -16949,7 +16961,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H455" s="8">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c t="s" r="I455" s="7">
         <v>27</v>
@@ -16962,7 +16974,7 @@
       </c>
       <c r="L455" s="7"/>
       <c t="s" r="M455" s="7">
-        <v>175</v>
+        <v>629</v>
       </c>
     </row>
     <row r="456" ht="14.25" customHeight="1">
@@ -16977,19 +16989,19 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F456" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G456" s="8">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c t="s" r="H456" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I456" s="7">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c t="s" r="J456" s="7">
         <v>273</v>
@@ -16999,7 +17011,7 @@
       </c>
       <c r="L456" s="7"/>
       <c t="s" r="M456" s="7">
-        <v>628</v>
+        <v>402</v>
       </c>
     </row>
     <row r="457" ht="14.25" customHeight="1">
@@ -17029,7 +17041,7 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F458" s="7">
         <v>321</v>
@@ -17044,12 +17056,12 @@
         <v>178</v>
       </c>
       <c t="s" r="J458" s="7">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
       <c t="s" r="M458" s="7">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="459" ht="14.25" customHeight="1">
@@ -17064,7 +17076,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F459" s="7">
         <v>321</v>
@@ -17084,7 +17096,7 @@
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
       <c t="s" r="M459" s="7">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="460" ht="15" customHeight="1">
@@ -17099,7 +17111,7 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F460" s="7">
         <v>321</v>
@@ -17108,20 +17120,20 @@
         <v>50</v>
       </c>
       <c t="s" r="H460" s="8">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c t="s" r="I460" s="7">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c t="s" r="J460" s="7">
         <v>156</v>
       </c>
       <c t="s" r="K460" s="7">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L460" s="7"/>
       <c t="s" r="M460" s="7">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="461" ht="14.25" customHeight="1">
@@ -17136,13 +17148,13 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F461" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G461" s="8">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c t="s" r="H461" s="8">
         <v>50</v>
@@ -17158,7 +17170,7 @@
       </c>
       <c r="L461" s="7"/>
       <c t="s" r="M461" s="7">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="462" ht="14.25" customHeight="1">
@@ -17188,7 +17200,7 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F463" s="7">
         <v>321</v>
@@ -17208,7 +17220,7 @@
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
       <c t="s" r="M463" s="7">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="464" ht="14.25" customHeight="1">
@@ -17223,7 +17235,7 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F464" s="7">
         <v>321</v>
@@ -17232,7 +17244,7 @@
         <v>143</v>
       </c>
       <c t="s" r="H464" s="8">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c t="s" r="I464" s="7">
         <v>205</v>
@@ -17243,7 +17255,7 @@
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
       <c t="s" r="M464" s="7">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="465" ht="15" customHeight="1">
@@ -17258,13 +17270,13 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F465" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G465" s="8">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c t="s" r="H465" s="8">
         <v>143</v>
@@ -17278,7 +17290,7 @@
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
       <c t="s" r="M465" s="7">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="466" ht="14.25" customHeight="1">
@@ -17308,7 +17320,7 @@
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F467" s="7">
         <v>321</v>
@@ -17323,12 +17335,12 @@
         <v>54</v>
       </c>
       <c t="s" r="J467" s="7">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K467" s="7"/>
       <c r="L467" s="7"/>
       <c t="s" r="M467" s="7">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="468" ht="14.25" customHeight="1">
@@ -17343,7 +17355,7 @@
       </c>
       <c r="D468" s="7"/>
       <c t="s" r="E468" s="7">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F468" s="7">
         <v>321</v>
@@ -17363,7 +17375,7 @@
       <c r="K468" s="7"/>
       <c r="L468" s="7"/>
       <c t="s" r="M468" s="7">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="469" ht="14.25" customHeight="1">
@@ -17378,7 +17390,7 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F469" s="7">
         <v>321</v>
@@ -17387,7 +17399,7 @@
         <v>50</v>
       </c>
       <c t="s" r="H469" s="8">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c t="s" r="I469" s="7">
         <v>61</v>
@@ -17398,7 +17410,7 @@
       <c r="K469" s="7"/>
       <c r="L469" s="7"/>
       <c t="s" r="M469" s="7">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="470" ht="15" customHeight="1">
@@ -17413,13 +17425,13 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F470" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G470" s="8">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c t="s" r="H470" s="8">
         <v>50</v>
@@ -17433,7 +17445,7 @@
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
       <c t="s" r="M470" s="7">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="471" ht="14.25" customHeight="1">
@@ -17448,7 +17460,7 @@
       </c>
       <c r="D471" s="7"/>
       <c t="s" r="E471" s="7">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F471" s="7">
         <v>321</v>
@@ -17483,7 +17495,7 @@
       </c>
       <c r="D472" s="7"/>
       <c t="s" r="E472" s="7">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F472" s="7">
         <v>321</v>
@@ -17531,7 +17543,7 @@
       </c>
       <c r="D474" s="7"/>
       <c t="s" r="E474" s="7">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F474" s="7">
         <v>321</v>
@@ -17543,15 +17555,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I474" s="7">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c t="s" r="J474" s="7">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K474" s="7"/>
       <c r="L474" s="7"/>
       <c t="s" r="M474" s="7">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="475" ht="15" customHeight="1">
@@ -17566,7 +17578,7 @@
       </c>
       <c r="D475" s="7"/>
       <c t="s" r="E475" s="7">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F475" s="7">
         <v>321</v>
@@ -17586,7 +17598,7 @@
       <c r="K475" s="7"/>
       <c r="L475" s="7"/>
       <c t="s" r="M475" s="7">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="476" ht="14.25" customHeight="1">
@@ -17601,7 +17613,7 @@
       </c>
       <c r="D476" s="7"/>
       <c t="s" r="E476" s="7">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F476" s="7">
         <v>321</v>
@@ -17619,11 +17631,11 @@
         <v>57</v>
       </c>
       <c t="s" r="K476" s="7">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L476" s="7"/>
       <c t="s" r="M476" s="7">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="477" ht="14.25" customHeight="1">
@@ -17638,7 +17650,7 @@
       </c>
       <c r="D477" s="7"/>
       <c t="s" r="E477" s="7">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F477" s="7">
         <v>321</v>
@@ -17660,7 +17672,7 @@
       </c>
       <c r="L477" s="7"/>
       <c t="s" r="M477" s="7">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="478" ht="14.25" customHeight="1">
@@ -17675,7 +17687,7 @@
       </c>
       <c r="D478" s="7"/>
       <c t="s" r="E478" s="7">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F478" s="7">
         <v>321</v>
@@ -17687,17 +17699,17 @@
         <v>301</v>
       </c>
       <c t="s" r="I478" s="7">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c t="s" r="J478" s="7">
         <v>201</v>
       </c>
       <c t="s" r="K478" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L478" s="7"/>
       <c t="s" r="M478" s="7">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="479" ht="14.25" customHeight="1">
@@ -17712,7 +17724,7 @@
       </c>
       <c r="D479" s="7"/>
       <c t="s" r="E479" s="7">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F479" s="7">
         <v>321</v>
@@ -17734,7 +17746,7 @@
       </c>
       <c r="L479" s="7"/>
       <c t="s" r="M479" s="7">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="480" ht="15" customHeight="1">
@@ -17749,7 +17761,7 @@
       </c>
       <c r="D480" s="7"/>
       <c t="s" r="E480" s="7">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F480" s="7">
         <v>321</v>
@@ -17764,14 +17776,14 @@
         <v>94</v>
       </c>
       <c t="s" r="J480" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c t="s" r="K480" s="7">
         <v>327</v>
       </c>
       <c r="L480" s="7"/>
       <c t="s" r="M480" s="7">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="481" ht="14.25" customHeight="1">
@@ -17801,7 +17813,7 @@
       </c>
       <c r="D482" s="7"/>
       <c t="s" r="E482" s="7">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F482" s="7">
         <v>320</v>
@@ -17813,7 +17825,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I482" s="7">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c t="s" r="J482" s="7">
         <v>36</v>
@@ -17821,7 +17833,7 @@
       <c r="K482" s="7"/>
       <c r="L482" s="7"/>
       <c t="s" r="M482" s="7">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="483" ht="14.25" customHeight="1">
@@ -17836,7 +17848,7 @@
       </c>
       <c r="D483" s="7"/>
       <c t="s" r="E483" s="7">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F483" s="7">
         <v>320</v>
@@ -17871,7 +17883,7 @@
       </c>
       <c r="D484" s="7"/>
       <c t="s" r="E484" s="7">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F484" s="7">
         <v>320</v>
@@ -17891,7 +17903,7 @@
       <c r="K484" s="7"/>
       <c r="L484" s="7"/>
       <c t="s" r="M484" s="7">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="485" ht="15" customHeight="1">
@@ -17906,7 +17918,7 @@
       </c>
       <c r="D485" s="7"/>
       <c t="s" r="E485" s="7">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F485" s="7">
         <v>320</v>
@@ -17915,7 +17927,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H485" s="8">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c t="s" r="I485" s="7">
         <v>61</v>
@@ -17926,7 +17938,7 @@
       <c r="K485" s="7"/>
       <c r="L485" s="7"/>
       <c t="s" r="M485" s="7">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="486" ht="14.25" customHeight="1">
@@ -17941,13 +17953,13 @@
       </c>
       <c r="D486" s="7"/>
       <c t="s" r="E486" s="7">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F486" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G486" s="8">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c t="s" r="H486" s="8">
         <v>232</v>
@@ -17969,14 +17981,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B487" s="7">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c t="s" r="C487" s="7">
         <v>14</v>
       </c>
       <c r="D487" s="7"/>
       <c t="s" r="E487" s="7">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F487" s="7">
         <v>320</v>
@@ -17996,7 +18008,7 @@
       <c r="K487" s="7"/>
       <c r="L487" s="7"/>
       <c t="s" r="M487" s="7">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="488" ht="14.25" customHeight="1">
@@ -18026,7 +18038,7 @@
       </c>
       <c r="D489" s="7"/>
       <c t="s" r="E489" s="7">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F489" s="7">
         <v>321</v>
@@ -18046,7 +18058,7 @@
       <c r="K489" s="7"/>
       <c r="L489" s="7"/>
       <c t="s" r="M489" s="7">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="490" ht="15" customHeight="1">
@@ -18061,7 +18073,7 @@
       </c>
       <c r="D490" s="7"/>
       <c t="s" r="E490" s="7">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F490" s="7">
         <v>321</v>
@@ -18070,7 +18082,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H490" s="8">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c t="s" r="I490" s="7">
         <v>172</v>
@@ -18081,7 +18093,7 @@
       <c r="K490" s="7"/>
       <c r="L490" s="7"/>
       <c t="s" r="M490" s="7">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="491" ht="14.25" customHeight="1">
@@ -18096,13 +18108,13 @@
       </c>
       <c r="D491" s="7"/>
       <c t="s" r="E491" s="7">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F491" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G491" s="8">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c t="s" r="H491" s="8">
         <v>21</v>
@@ -18116,7 +18128,7 @@
       <c r="K491" s="7"/>
       <c r="L491" s="7"/>
       <c t="s" r="M491" s="7">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="492" ht="14.25" customHeight="1">
@@ -18131,7 +18143,7 @@
       </c>
       <c r="D492" s="7"/>
       <c t="s" r="E492" s="7">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F492" s="7">
         <v>321</v>
@@ -18146,11 +18158,13 @@
         <v>285</v>
       </c>
       <c t="s" r="J492" s="7">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K492" s="7"/>
       <c r="L492" s="7"/>
-      <c r="M492" s="7"/>
+      <c t="s" r="M492" s="7">
+        <v>629</v>
+      </c>
     </row>
     <row r="493" ht="14.25" customHeight="1">
       <c r="A493" s="6"/>
@@ -18179,7 +18193,7 @@
       </c>
       <c r="D494" s="7"/>
       <c t="s" r="E494" s="7">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="F494" s="7">
         <v>321</v>
@@ -18191,7 +18205,7 @@
         <v>336</v>
       </c>
       <c t="s" r="I494" s="7">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c t="s" r="J494" s="7">
         <v>303</v>
@@ -18214,7 +18228,7 @@
       </c>
       <c r="D495" s="7"/>
       <c t="s" r="E495" s="7">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="F495" s="7">
         <v>321</v>
@@ -18249,7 +18263,7 @@
       </c>
       <c r="D496" s="7"/>
       <c t="s" r="E496" s="7">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="F496" s="7">
         <v>321</v>
@@ -18269,7 +18283,7 @@
       <c r="K496" s="7"/>
       <c r="L496" s="7"/>
       <c t="s" r="M496" s="7">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="497" ht="14.25" customHeight="1">
@@ -18284,7 +18298,7 @@
       </c>
       <c r="D497" s="7"/>
       <c t="s" r="E497" s="7">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="F497" s="7">
         <v>321</v>
@@ -18299,12 +18313,12 @@
         <v>110</v>
       </c>
       <c t="s" r="J497" s="7">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="K497" s="7"/>
       <c r="L497" s="7"/>
       <c t="s" r="M497" s="7">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="498" ht="14.25" customHeight="1">
@@ -18334,7 +18348,7 @@
       </c>
       <c r="D499" s="7"/>
       <c t="s" r="E499" s="7">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F499" s="7">
         <v>320</v>
@@ -18354,7 +18368,7 @@
       <c r="K499" s="7"/>
       <c r="L499" s="7"/>
       <c t="s" r="M499" s="7">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="500" ht="15" customHeight="1">
@@ -18369,7 +18383,7 @@
       </c>
       <c r="D500" s="7"/>
       <c t="s" r="E500" s="7">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F500" s="7">
         <v>320</v>
@@ -18384,12 +18398,12 @@
         <v>233</v>
       </c>
       <c t="s" r="J500" s="7">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K500" s="7"/>
       <c r="L500" s="7"/>
       <c t="s" r="M500" s="7">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="501" ht="14.25" customHeight="1">
@@ -18404,7 +18418,7 @@
       </c>
       <c r="D501" s="7"/>
       <c t="s" r="E501" s="7">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F501" s="7">
         <v>320</v>
@@ -18424,7 +18438,7 @@
       <c r="K501" s="7"/>
       <c r="L501" s="7"/>
       <c t="s" r="M501" s="7">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="502" ht="14.25" customHeight="1">
@@ -18439,7 +18453,7 @@
       </c>
       <c r="D502" s="7"/>
       <c t="s" r="E502" s="7">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F502" s="7">
         <v>320</v>
@@ -18451,7 +18465,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I502" s="7">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c t="s" r="J502" s="7">
         <v>43</v>
@@ -18476,7 +18490,7 @@
       </c>
       <c r="D503" s="7"/>
       <c t="s" r="E503" s="7">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F503" s="7">
         <v>320</v>
@@ -18513,7 +18527,7 @@
       </c>
       <c r="D504" s="7"/>
       <c t="s" r="E504" s="7">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F504" s="7">
         <v>320</v>
@@ -18528,10 +18542,10 @@
         <v>239</v>
       </c>
       <c t="s" r="J504" s="7">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c t="s" r="K504" s="7">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="L504" s="7"/>
       <c t="s" r="M504" s="7">
@@ -18565,7 +18579,7 @@
       </c>
       <c r="D506" s="7"/>
       <c t="s" r="E506" s="7">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F506" s="7">
         <v>330</v>
@@ -18574,7 +18588,7 @@
         <v>143</v>
       </c>
       <c t="s" r="H506" s="8">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c t="s" r="I506" s="7">
         <v>183</v>
@@ -18600,13 +18614,13 @@
       </c>
       <c r="D507" s="7"/>
       <c t="s" r="E507" s="7">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F507" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G507" s="8">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c t="s" r="H507" s="8">
         <v>143</v>
@@ -18648,13 +18662,13 @@
       </c>
       <c r="D509" s="7"/>
       <c t="s" r="E509" s="7">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="F509" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G509" s="8">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c t="s" r="H509" s="8">
         <v>143</v>
@@ -18666,11 +18680,11 @@
         <v>138</v>
       </c>
       <c t="s" r="K509" s="7">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L509" s="7"/>
       <c t="s" r="M509" s="7">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="510" ht="15" customHeight="1">
@@ -18685,7 +18699,7 @@
       </c>
       <c r="D510" s="7"/>
       <c t="s" r="E510" s="7">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="F510" s="7">
         <v>330</v>
@@ -18694,10 +18708,10 @@
         <v>143</v>
       </c>
       <c t="s" r="H510" s="8">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c t="s" r="I510" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c t="s" r="J510" s="7">
         <v>18</v>
@@ -18705,7 +18719,7 @@
       <c r="K510" s="7"/>
       <c r="L510" s="7"/>
       <c t="s" r="M510" s="7">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="511" ht="14.25" customHeight="1">
@@ -18735,7 +18749,7 @@
       </c>
       <c r="D512" s="7"/>
       <c t="s" r="E512" s="7">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F512" s="7">
         <v>330</v>
@@ -18744,7 +18758,7 @@
         <v>143</v>
       </c>
       <c t="s" r="H512" s="8">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c t="s" r="I512" s="7">
         <v>183</v>
@@ -18770,13 +18784,13 @@
       </c>
       <c r="D513" s="7"/>
       <c t="s" r="E513" s="7">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F513" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G513" s="8">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c t="s" r="H513" s="8">
         <v>143</v>
@@ -18818,7 +18832,7 @@
       </c>
       <c r="D515" s="7"/>
       <c t="s" r="E515" s="7">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="F515" s="7">
         <v>330</v>
@@ -18827,10 +18841,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H515" s="8">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c t="s" r="I515" s="7">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c t="s" r="J515" s="7">
         <v>39</v>
@@ -18870,7 +18884,7 @@
       </c>
       <c r="D517" s="7"/>
       <c t="s" r="E517" s="7">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F517" s="7">
         <v>330</v>
@@ -18885,10 +18899,10 @@
         <v>233</v>
       </c>
       <c t="s" r="J517" s="7">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c t="s" r="K517" s="7">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L517" s="7"/>
       <c t="s" r="M517" s="7">
@@ -18907,7 +18921,7 @@
       </c>
       <c r="D518" s="7"/>
       <c t="s" r="E518" s="7">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F518" s="7">
         <v>330</v>
@@ -18916,18 +18930,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H518" s="8">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c t="s" r="I518" s="7">
         <v>159</v>
       </c>
       <c t="s" r="J518" s="7">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K518" s="7"/>
       <c r="L518" s="7"/>
       <c t="s" r="M518" s="7">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="519" ht="14.25" customHeight="1">
@@ -18957,7 +18971,7 @@
       </c>
       <c r="D520" s="7"/>
       <c t="s" r="E520" s="7">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="F520" s="7">
         <v>330</v>
@@ -18969,7 +18983,7 @@
         <v>91</v>
       </c>
       <c t="s" r="I520" s="7">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c t="s" r="J520" s="7">
         <v>194</v>
@@ -18977,7 +18991,7 @@
       <c r="K520" s="7"/>
       <c r="L520" s="7"/>
       <c t="s" r="M520" s="7">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="521" ht="14.25" customHeight="1">
@@ -18985,14 +18999,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B521" s="7">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c t="s" r="C521" s="7">
         <v>14</v>
       </c>
       <c r="D521" s="7"/>
       <c t="s" r="E521" s="7">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="F521" s="7">
         <v>330</v>
@@ -19001,7 +19015,7 @@
         <v>91</v>
       </c>
       <c t="s" r="H521" s="8">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c t="s" r="I521" s="7">
         <v>22</v>
@@ -19014,7 +19028,7 @@
       </c>
       <c r="L521" s="7"/>
       <c t="s" r="M521" s="7">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="522" ht="14.25" customHeight="1">
@@ -19029,13 +19043,13 @@
       </c>
       <c r="D522" s="7"/>
       <c t="s" r="E522" s="7">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="F522" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G522" s="8">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c t="s" r="H522" s="8">
         <v>91</v>
@@ -19048,7 +19062,9 @@
       </c>
       <c r="K522" s="7"/>
       <c r="L522" s="7"/>
-      <c r="M522" s="7"/>
+      <c t="s" r="M522" s="7">
+        <v>686</v>
+      </c>
     </row>
     <row r="523" ht="14.25" customHeight="1">
       <c r="A523" s="6"/>
@@ -19077,7 +19093,7 @@
       </c>
       <c r="D524" s="7"/>
       <c t="s" r="E524" s="7">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="F524" s="7">
         <v>330</v>
@@ -19086,7 +19102,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H524" s="8">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c t="s" r="I524" s="7">
         <v>152</v>
@@ -19112,13 +19128,13 @@
       </c>
       <c r="D525" s="7"/>
       <c t="s" r="E525" s="7">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="F525" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G525" s="8">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c t="s" r="H525" s="8">
         <v>21</v>
@@ -19127,17 +19143,17 @@
         <v>29</v>
       </c>
       <c t="s" r="J525" s="7">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K525" s="7"/>
       <c r="L525" s="7"/>
       <c t="s" r="M525" s="7">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="526" ht="15.75" customHeight="1">
       <c t="s" r="A526" s="9">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B526" s="9"/>
       <c r="C526" s="9"/>
@@ -19157,7 +19173,7 @@
     <row r="527" ht="65.25" customHeight="1"/>
     <row r="528" ht="16.5" customHeight="1">
       <c t="s" r="A528" s="10">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B528" s="10"/>
       <c r="C528" s="10"/>
@@ -19170,7 +19186,7 @@
       <c r="J528" s="10"/>
       <c r="K528" s="10"/>
       <c t="s" r="L528" s="11">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="M528" s="11"/>
       <c r="N528" s="11"/>
